--- a/logs/trade_log.xlsx
+++ b/logs/trade_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN2"/>
+  <dimension ref="A1:AN15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,16 +657,6 @@
           <t>none</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
         <v>20</v>
       </c>
@@ -675,10 +665,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
       <c r="Y2" t="n">
         <v>0.5806</v>
       </c>
@@ -731,6 +717,1214 @@
       <c r="AN2" t="inlineStr">
         <is>
           <t>sent</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-04T14:20:37.639509+00:00</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-05-04_14-20-37</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>DRY_RUN</t>
+        </is>
+      </c>
+      <c r="D3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>50</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>20</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Sin datos de mercado</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-04T15:20:37.642872+00:00</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-05-04_15-20-37</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>DRY_RUN</t>
+        </is>
+      </c>
+      <c r="D4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>50</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Sin datos de mercado</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-04T16:20:37.640889+00:00</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-05-04_16-20-37</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>DRY_RUN</t>
+        </is>
+      </c>
+      <c r="D5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>50</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Sin datos de mercado</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-04T17:20:37.646036+00:00</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-05-04_17-20-37</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>DRY_RUN</t>
+        </is>
+      </c>
+      <c r="D6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>50</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Sin datos de mercado</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-04T18:20:37.642218+00:00</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-05-04_18-20-37</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>DRY_RUN</t>
+        </is>
+      </c>
+      <c r="D7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>50</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Sin datos de mercado</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-04T19:20:37.634593+00:00</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-05-04_19-20-37</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DRY_RUN</t>
+        </is>
+      </c>
+      <c r="D8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>NO_DATA</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>50</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Sin datos de mercado</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-05T13:48:21.775001+00:00</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-05-05_13-48-21</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>DRY_RUN</t>
+        </is>
+      </c>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>ANALYZED</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>NO_SIGNAL</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>50</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.5675</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>Total weighted score of 0.5619 falls significantly below the 0.72 approval threshold, and only 3 of 6 dimensions exceed the 0.55 passing bar (need ≥5). While Events score strongly at 0.92 and Cross-Assets is bullish at 0.60, critical weakness in Technical (0.45) and Components (0.50) indicates insufficient conviction for a swing-trade entry. Hold for better risk/reward alignment.</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.5619</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Score 0.562 &lt; umbral 0.72</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-05T14:48:21.776006+00:00</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-05-05_14-48-21</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>DRY_RUN</t>
+        </is>
+      </c>
+      <c r="D10" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ANALYZED</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>NO_SIGNAL</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>50</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.5675</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>Total weighted score of 0.5619 falls well below the 0.72 approval threshold. Only 3 of 6 dimensions pass the 0.55 hurdle (Macro, Events, Cross-Assets), failing the requirement of at least 5 passing dimensions. Technical (0.45) and Components (0.50) weakness, combined with neutral Sentiment (0.52), indicate insufficient conviction for swing-trade entry despite favorable event setup.</t>
+        </is>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.5619</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Score 0.562 &lt; umbral 0.72</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-05-05T15:48:21.785111+00:00</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-05-05_15-48-21</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>DRY_RUN</t>
+        </is>
+      </c>
+      <c r="D11" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ANALYZED</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>NO_SIGNAL</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>50</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.5675</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>Total weighted score of 0.562 falls significantly below the 0.72 approval threshold. Only 3 of 6 dimensions exceed the 0.55 minimum, with Technical (0.45) and Components (0.50) notably weak. While Events scores well at 0.92, insufficient breadth across macro, technical, and sentiment dimensions prevents entry. Recommend waiting for multi-dimensional confirmation before initiating long SPY position.</t>
+        </is>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.5619</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Score 0.562 &lt; umbral 0.72</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-05-05T16:48:21.773535+00:00</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-05-05_16-48-21</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>DRY_RUN</t>
+        </is>
+      </c>
+      <c r="D12" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ANALYZED</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>NO_SIGNAL</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>50</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.5675</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>Total weighted score 0.5619 falls significantly below the 0.72 approval threshold. Only 3 of 6 dimensions pass the 0.55 hurdle; Technical (0.45), Components (0.50), and Sentiment (0.52) are all sub-threshold, indicating weak conviction across price action, sector breadth, and market psychology. Despite favorable Events (0.92) and Cross-Assets (0.60), the weight of neutral-to-weak signals in Macro, Technical, and Components does not support a swing-long initiation at this time.</t>
+        </is>
+      </c>
+      <c r="AH12" t="n">
+        <v>0.5619</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Score 0.562 &lt; umbral 0.72</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-05-05T17:48:21.782438+00:00</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-05-05_17-48-21</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>DRY_RUN</t>
+        </is>
+      </c>
+      <c r="D13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ANALYZED</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>NO_SIGNAL</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>50</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.5675</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>Total weighted score of 0.5619 falls significantly below the 0.72 approval threshold. Only 3 of 6 dimensions pass the 0.55 floor, with Technical (0.45), Components (0.50), and Macro (0.5675) all subthreshold, indicating weak conviction. Despite favorable Events (0.92) and Cross-Assets (0.60), insufficient bullish alignment across momentum, fundamentals, and sector breadth warrants staying in dry-run mode.</t>
+        </is>
+      </c>
+      <c r="AH13" t="n">
+        <v>0.5619</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Score 0.562 &lt; umbral 0.72</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-05-05T18:48:21.780424+00:00</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-05-05_18-48-21</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>DRY_RUN</t>
+        </is>
+      </c>
+      <c r="D14" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ANALYZED</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>NO_SIGNAL</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>50</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="S14" t="n">
+        <v>20</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.5675</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>Total weighted score of 0.562 falls significantly below the 0.72 approval threshold. Only 3 of 6 dimensions pass the 0.55 hurdle; Technical (0.45), Components (0.50), and Sentiment (0.52) are all subthreshold, indicating weak momentum, sector rotation concerns, and unfavorable risk sentiment. Despite favorable Events (0.92) and solid Cross-Assets (0.60), the confluence of weak technicals and neutral macro/sentiment does not warrant a long initiation in this high-VIX regime.</t>
+        </is>
+      </c>
+      <c r="AH14" t="n">
+        <v>0.5619</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Score 0.562 &lt; umbral 0.72</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-05-05T19:48:21.785379+00:00</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-05-05_19-48-21</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>DRY_RUN</t>
+        </is>
+      </c>
+      <c r="D15" t="b">
+        <v>0</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ANALYZED</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>NO_SIGNAL</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>50</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="n">
+        <v>0.5675</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>Total weighted score of 0.5619 falls significantly below the 0.72 approval threshold. Only 3 of 6 dimensions pass the 0.55 hurdle; Technical (0.45), Components (0.50), and Macro (0.5675) are all too weak to support a long entry despite favorable Events (0.92) and acceptable Cross-Assets (0.60). Market conditions remain structurally neutral with insufficient multi-dimensional confirmation.</t>
+        </is>
+      </c>
+      <c r="AH15" t="n">
+        <v>0.5619</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Score 0.562 &lt; umbral 0.72</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>n/a</t>
         </is>
       </c>
     </row>
